--- a/data/trans_orig/IP25B01_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>31310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36217</t>
+          <t>35197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35945</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50665</t>
+          <t>49943</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40651</t>
+          <t>41557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65134</t>
+          <t>64739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>79331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108922</t>
+          <t>108616</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>34083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>50494</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43442</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66144</t>
+          <t>66527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85414</t>
+          <t>83586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113628</t>
+          <t>111489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18732</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>20143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36777</t>
+          <t>37079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30664</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>46498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65849</t>
+          <t>66923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89204</t>
+          <t>90105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>28511</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>43846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32191</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47992</t>
+          <t>48587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65266</t>
+          <t>65051</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87835</t>
+          <t>87423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>29638</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49222</t>
+          <t>50094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14686</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27212</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32459</t>
+          <t>32284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36641</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>55454</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105710</t>
+          <t>104556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40668</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36589</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142638</t>
+          <t>146067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>25150</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>74050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47892</t>
+          <t>49610</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93367</t>
+          <t>91451</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70901</t>
+          <t>71095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>100678</t>
+          <t>100941</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126874</t>
+          <t>129568</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>181802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,19%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49185</t>
+          <t>47089</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94455</t>
+          <t>92787</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58484</t>
+          <t>59289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85993</t>
+          <t>85669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117778</t>
+          <t>118284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169831</t>
+          <t>170883</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59910</t>
+          <t>56122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27904</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74856</t>
+          <t>71421</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31773</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57085</t>
+          <t>57094</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35139</t>
+          <t>34191</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52155</t>
+          <t>51870</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46771</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73915</t>
+          <t>73974</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87129</t>
+          <t>89441</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120221</t>
+          <t>120915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>29697</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36464</t>
+          <t>37592</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60968</t>
+          <t>62126</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>71624</t>
+          <t>72500</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>102496</t>
+          <t>102902</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>35225</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51278</t>
+          <t>52000</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>71904</t>
+          <t>71570</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>33313</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34996</t>
+          <t>35825</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62892</t>
+          <t>63681</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>146255</t>
+          <t>149533</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>55421</t>
+          <t>54542</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>112305</t>
+          <t>114155</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107569</t>
+          <t>107260</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>231653</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>74089</t>
+          <t>75101</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>110346</t>
+          <t>111274</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>86062</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>122783</t>
+          <t>121523</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>171738</t>
+          <t>173204</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>222288</t>
+          <t>222649</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>208019</t>
+          <t>207381</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>271153</t>
+          <t>268564</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>265492</t>
+          <t>266792</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>320447</t>
+          <t>320708</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>493340</t>
+          <t>489103</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>573772</t>
+          <t>575723</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>202380</t>
+          <t>206155</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>262401</t>
+          <t>261254</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>244379</t>
+          <t>245870</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>296120</t>
+          <t>297239</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>469111</t>
+          <t>465469</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>546037</t>
+          <t>547159</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B01_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos entre semana / solo 2023 en 2023 (tasa de respuesta: 98,33%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos entre semana en 2023 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13554</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4411</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9784</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31310</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35197</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8896</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22534</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13065</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7873</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19108</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48040</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38240</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>58065</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>39,73%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>31,62%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>48,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>41317</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33556</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>49943</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>33,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52620</t>
+          <t>40472</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41557</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64739</t>
+          <t>48995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>93937</t>
+          <t>88513</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79331</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108616</t>
+          <t>102059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51150</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41742</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>62085</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>42486</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>34083</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>50494</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>41,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>33149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66527</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>98113</t>
+          <t>92766</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83586</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111489</t>
+          <t>105090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>120932</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>120932</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>120932</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>135196</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135196</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135196</t>
+          <t>99980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>236474</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236474</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236474</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6699</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9634</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14080</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8732</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21531</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12171</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7552</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18804</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22111</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37079</t>
+          <t>36322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37143</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29253</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45728</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>39709</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47876</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42,85%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46498</t>
+          <t>49096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>77545</t>
+          <t>78287</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66923</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90105</t>
+          <t>90491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37743</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29175</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>50,57%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>36170</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28511</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43846</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>39,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>47,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40152</t>
+          <t>36051</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32171</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>43953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>73795</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>62426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87423</t>
+          <t>85445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>92670</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>92670</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>92670</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94669</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>94669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>186067</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>186067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>186067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7583</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3222</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1173</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6966</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12349</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7677</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>19461</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>21,69%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>34,18%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9272</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>4910</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19998</t>
+          <t>20272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>31749</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20662</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27584</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17993</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24389</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40129</t>
+          <t>39891</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>31369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50094</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20650</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26284</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20705</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14715</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26733</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>40,45%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32284</t>
+          <t>25868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>45763</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>31674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55454</t>
+          <t>48854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>51192</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51192</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>51192</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>52835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>109775</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>109775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>109775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15465</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>39323</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>40284</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>13681</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>104556</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>48,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>26198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>65274</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146067</t>
+          <t>58075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>31742</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22706</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>41829</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>24246</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14626</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>36033</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46029</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>58447</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>41744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74050</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>79041</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65755</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>93294</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>39,48%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>32,85%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>74526</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>49610</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>91451</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>34,74%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>42,63%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85235</t>
+          <t>69383</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71095</t>
+          <t>59177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>100941</t>
+          <t>80503</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>159762</t>
+          <t>148423</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>129568</t>
+          <t>130888</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>181802</t>
+          <t>166232</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>65341</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>53884</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>78027</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>32,64%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>38,98%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>75470</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>47089</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>92787</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>71917</t>
+          <t>67345</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59289</t>
+          <t>57099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85669</t>
+          <t>77213</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>147387</t>
+          <t>132686</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118284</t>
+          <t>117140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170883</t>
+          <t>150548</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>200185</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>200185</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>200185</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>214527</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>214527</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>214527</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>216342</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216342</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216342</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>430869</t>
+          <t>375459</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>430869</t>
+          <t>375459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>430869</t>
+          <t>375459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26315</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>16181</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>50812</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>12240</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>7695</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>18772</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28952</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56122</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>38943</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27747</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71421</t>
+          <t>64692</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>18229</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11739</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>25873</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>22931</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>15683</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>34224</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>29,37%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>42901</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>30048</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57094</t>
+          <t>50739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>56367</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>43874</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>68584</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>30,19%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>47,19%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>43036</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>34191</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>51870</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>44,51%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>44865</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73974</t>
+          <t>53801</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>104679</t>
+          <t>101232</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89441</t>
+          <t>86522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120915</t>
+          <t>115057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>44417</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>33580</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55446</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>30,56%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>38,15%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>38318</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>29697</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>47177</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>32,88%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>49173</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62126</t>
+          <t>46539</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>87491</t>
+          <t>81702</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>72500</t>
+          <t>67801</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>102902</t>
+          <t>96381</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>145328</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>145328</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>145328</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>116525</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>116525</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>116525</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>159738</t>
+          <t>115979</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>159738</t>
+          <t>115979</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159738</t>
+          <t>115979</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>276263</t>
+          <t>261307</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>276263</t>
+          <t>261307</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>276263</t>
+          <t>261307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>829</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -3678,72 +3678,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>6738</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>12325</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>10157</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>6037</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>15922</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
+          <t>16,13%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>26148</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>33881</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>26877</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>41582</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>49,85%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>39,55%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>61,18%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>28127</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>21301</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>35225</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>42,11%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>31,89%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>52,73%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>37611</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>61431</t>
+          <t>64129</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52000</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>71570</t>
+          <t>73873</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>25342</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35825</t>
+          <t>31355</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>53075</t>
+          <t>47282</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43456</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>63681</t>
+          <t>57996</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>66799</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>66799</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>66799</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>71613</t>
+          <t>68416</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>136381</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>136381</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>136381</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>67167</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>50453</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>96962</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>67952</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>39237</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>149533</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>76174</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>114155</t>
+          <t>60550</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>144126</t>
+          <t>112376</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107260</t>
+          <t>92132</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>246871</t>
+          <t>142080</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>97637</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>82662</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>115048</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>91842</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>75101</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>111274</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>103706</t>
+          <t>91190</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>86062</t>
+          <t>77098</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>121523</t>
+          <t>107508</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>195548</t>
+          <t>188827</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>173204</t>
+          <t>166923</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>222649</t>
+          <t>210473</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>275133</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>249332</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>298647</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>43,74%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>361</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>244708</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>207381</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>268564</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>38,06%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>32,25%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>292775</t>
+          <t>245342</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>266792</t>
+          <t>227166</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>320708</t>
+          <t>266575</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>537483</t>
+          <t>520474</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>489103</t>
+          <t>488709</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>575723</t>
+          <t>552675</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>242810</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>218762</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>266260</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>35,56%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>32,04%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>364</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>238491</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>206155</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>261254</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>40,63%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>269659</t>
+          <t>225414</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>245870</t>
+          <t>205229</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>297239</t>
+          <t>246047</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>508150</t>
+          <t>468224</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>465469</t>
+          <t>440884</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>547159</t>
+          <t>499111</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>682748</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>682748</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>682748</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>906</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>642992</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>642992</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>642992</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>742314</t>
+          <t>607154</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>742314</t>
+          <t>607154</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>742314</t>
+          <t>607154</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1385306</t>
+          <t>1289901</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1385306</t>
+          <t>1289901</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1385306</t>
+          <t>1289901</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
